--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.173.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.173.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.173.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.173.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 146 â€” 147</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 146â€”147</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]166</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]166</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L12: isolated marker/symbol line :: 166</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L15: isolated marker/symbol line :: w</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]166</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L154: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 65</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,24 +676,24 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ na to hear Judgment to be served se</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：.</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: 7</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L44: symbol-only separator/garbage line :: 7. 13</t>
+          <t>L15: isolated marker/symbol line :: w</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -727,24 +735,24 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€‚ã€�</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。、</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 49â€”50</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L17: isolated marker/symbol line :: 13</t>
+          <t>L16: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 13</t>
+          <t>L44: symbol-only separator/garbage line :: 7. 13</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,12 +778,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -786,24 +794,24 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L88: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 13</t>
+          <t>L17: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L50: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. . 15</t>
+          <t>L46: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -843,22 +851,26 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L20: isolated marker/symbol line :: 15</t>
+          <t>L18: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L54: symbol-only separator/garbage line :: . 110</t>
+          <t>L50: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. . 15</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -898,22 +910,26 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L22: symbol-only separator/garbage line :: . 110</t>
+          <t>L20: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L54: symbol-only separator/garbage line :: . 110</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -956,19 +972,19 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L127: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: W</t>
+          <t>L22: symbol-only separator/garbage line :: . 110</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: M</t>
+          <t>L55: symbol-only separator/garbage line :: 146—147</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1007,19 +1023,19 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L129: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: Ï‰</t>
+          <t>L23: symbol-only separator/garbage line :: 146 — 147</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: R</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1041,12 +1057,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1058,19 +1074,19 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L129: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢</t>
+          <t>L133: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: d</t>
+          <t>L31: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: T</t>
+          <t>L60: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1097,7 +1113,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1109,19 +1125,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L154: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 65</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 48</t>
+          <t>L36: isolated marker/symbol line :: ω</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 48</t>
+          <t>L64: isolated marker/symbol line :: R</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1143,12 +1159,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1160,19 +1176,19 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 65</t>
+          <t>L166: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: 48</t>
+          <t>L41: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 48</t>
+          <t>L68: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1209,21 +1225,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 65â€”66</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 49</t>
+          <t>L49: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 49</t>
+          <t>L70: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1250,7 +1262,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1260,21 +1272,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 49</t>
+          <t>L50: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 49</t>
+          <t>L72: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1316,12 +1324,12 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L54: symbol-only separator/garbage line :: 49-50</t>
+          <t>L51: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 49</t>
+          <t>L74: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1363,12 +1371,12 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 49</t>
+          <t>L52: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L82: symbol-only separator/garbage line :: .50</t>
+          <t>L76: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1410,12 +1418,12 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: d</t>
+          <t>L54: symbol-only separator/garbage line :: 49-50</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 50</t>
+          <t>L78: symbol-only separator/garbage line :: . 49—50</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1445,12 +1453,12 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 50</t>
+          <t>L55: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L80: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1480,12 +1488,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 50.</t>
+          <t>L56: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1515,12 +1523,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 109</t>
+          <t>L57: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L84: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1550,12 +1558,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 111</t>
+          <t>L59: symbol-only separator/garbage line :: 50.</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1585,12 +1593,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: E</t>
+          <t>L61: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: a</t>
+          <t>L88: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1620,12 +1628,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: M</t>
+          <t>L62: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1655,12 +1663,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: R</t>
+          <t>L63: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: Â»</t>
+          <t>L92: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1690,12 +1698,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: T</t>
+          <t>L64: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L96: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1725,12 +1733,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: A</t>
+          <t>L66: isolated marker/symbol line :: R</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L135: isolated marker/symbol line :: A</t>
+          <t>L127: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1760,12 +1768,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: A</t>
+          <t>L68: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: -A</t>
+          <t>L129: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1795,12 +1803,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: T</t>
+          <t>L69: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: T</t>
+          <t>L131: isolated marker/symbol line :: »</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1830,12 +1838,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: M</t>
+          <t>L70: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L141: isolated marker/symbol line :: M</t>
+          <t>L133: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1865,12 +1873,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: C</t>
+          <t>L72: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: C</t>
+          <t>L135: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1900,12 +1908,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: M</t>
+          <t>L73: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: M</t>
+          <t>L137: isolated marker/symbol line :: -A</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1935,12 +1943,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: S</t>
+          <t>L74: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L145: isolated marker/symbol line :: s</t>
+          <t>L140: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1970,12 +1978,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 5</t>
+          <t>L75: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: s</t>
+          <t>L141: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2005,12 +2013,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L76: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L148: symbol-only separator/garbage line :: . 109</t>
+          <t>L142: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2040,12 +2048,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 1</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：.</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: 111</t>
+          <t>L144: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2075,12 +2083,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 65</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。、</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L152: symbol-only separator/garbage line :: - . 65</t>
+          <t>L145: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2110,12 +2118,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: "</t>
+          <t>L84: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L158: isolated marker/symbol line :: 66</t>
+          <t>L146: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2145,12 +2153,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L100: symbol-only separator/garbage line :: . 65</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L159: symbol-only separator/garbage line :: .66</t>
+          <t>L148: symbol-only separator/garbage line :: . 109</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2180,12 +2188,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 65</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L150: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2215,12 +2223,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L102: symbol-only separator/garbage line :: 65-66</t>
+          <t>L95: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L168: isolated marker/symbol line :: E</t>
+          <t>L152: symbol-only separator/garbage line :: - . 65</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2250,12 +2258,12 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 66</t>
+          <t>L96: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: F</t>
+          <t>L154: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 65</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2285,12 +2293,12 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 66</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L170: isolated marker/symbol line :: V</t>
+          <t>L156: symbol-only separator/garbage line :: . 65—66</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2320,12 +2328,12 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 67</t>
+          <t>L99: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L171: isolated marker/symbol line :: 8</t>
+          <t>L158: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2355,10 +2363,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 108</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L100: symbol-only separator/garbage line :: . 65</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L159: symbol-only separator/garbage line :: .66</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2386,10 +2398,14 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: S</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L101: isolated marker/symbol line :: 65</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L166: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2417,10 +2433,14 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: 7</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L102: symbol-only separator/garbage line :: 65-66</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L168: isolated marker/symbol line :: E</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2448,10 +2468,14 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: E</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L103: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L169: isolated marker/symbol line :: F</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2479,10 +2503,14 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: F</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr"/>
+          <t>L104: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L170: isolated marker/symbol line :: V</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
       <c r="R48" s="1" t="inlineStr"/>
@@ -2494,6 +2522,196 @@
       <c r="X48" s="1" t="inlineStr"/>
       <c r="Y48" s="1" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="1" t="inlineStr"/>
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr"/>
+      <c r="H49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr"/>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
+      <c r="L49" s="1" t="inlineStr"/>
+      <c r="M49" s="1" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>L106: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>L171: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="R49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr"/>
+      <c r="V49" s="1" t="inlineStr"/>
+      <c r="W49" s="1" t="inlineStr"/>
+      <c r="X49" s="1" t="inlineStr"/>
+      <c r="Y49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
+      <c r="H50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
+      <c r="L50" s="1" t="inlineStr"/>
+      <c r="M50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>L107: isolated marker/symbol line :: 108</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr"/>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr"/>
+      <c r="V50" s="1" t="inlineStr"/>
+      <c r="W50" s="1" t="inlineStr"/>
+      <c r="X50" s="1" t="inlineStr"/>
+      <c r="Y50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L108: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L109: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L110: isolated marker/symbol line :: E</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>L111: isolated marker/symbol line :: F</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr"/>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+      <c r="W54" s="1" t="inlineStr"/>
+      <c r="X54" s="1" t="inlineStr"/>
+      <c r="Y54" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
